--- a/Data100.xlsx
+++ b/Data100.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cityuni-my.sharepoint.com/personal/allel_kechida_city_ac_uk/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kechi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="8_{0C65FBF2-AF10-4950-A460-763DCF45D5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE04E875-6F47-49FE-9E77-7774B90109C9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6675555-13B7-4DBC-B58C-3728944D0F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{131766D7-03E8-4ABE-966F-E54EA5032F95}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="25">
   <si>
     <t>Attempts</t>
   </si>
@@ -56,31 +56,64 @@
     <t>Resurrection used?</t>
   </si>
   <si>
-    <t>phase 1</t>
-  </si>
-  <si>
-    <t>death</t>
-  </si>
-  <si>
-    <t>missed deflection</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>failed sweep counter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phase 0 </t>
-  </si>
-  <si>
-    <t>Focus on improvement</t>
-  </si>
-  <si>
-    <t>N/A</t>
+    <t>How well I applied it</t>
+  </si>
+  <si>
+    <t>Phase 1</t>
+  </si>
+  <si>
+    <t>Phase 0</t>
+  </si>
+  <si>
+    <t>Defeat</t>
+  </si>
+  <si>
+    <t>Missed deflection</t>
+  </si>
+  <si>
+    <t>Failed sweep counter</t>
+  </si>
+  <si>
+    <t>Posture broken</t>
+  </si>
+  <si>
+    <t>Deflections</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>Furthest Phase</t>
+  </si>
+  <si>
+    <t>Sweep attacks</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>improvement focus</t>
+  </si>
+  <si>
+    <t>Posture management</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>Failed Mikiri Counter</t>
+  </si>
+  <si>
+    <t>Mikiri Counters</t>
+  </si>
+  <si>
+    <t>Missed dodge</t>
+  </si>
+  <si>
+    <t>General Survival</t>
+  </si>
+  <si>
+    <t>Phase 2</t>
   </si>
 </sst>
 </file>
@@ -125,7 +158,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="17">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -183,15 +228,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11D32975-C8F7-4E4C-9DCB-E1DD0F4EF809}" name="Table1" displayName="Table1" ref="A1:F100" totalsRowShown="0" dataDxfId="12">
-  <autoFilter ref="A1:F100" xr:uid="{11D32975-C8F7-4E4C-9DCB-E1DD0F4EF809}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{ECCC568F-30EE-4B6A-B426-3426F99425E7}" name="Attempts" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{16429E15-314C-4930-A463-A56B94D5D37F}" name="Phases" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{EA75679D-0C9D-4438-A7AA-74FB81AF92ED}" name="Result" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{BA7551D7-01AC-42E1-A8FB-050E702D3911}" name="Cause of Death" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{87E6156D-9D22-48BA-909B-ED2CF9E0F3B4}" name="Resurrection used?" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{232FD259-656D-4902-889A-854F57D8DE67}" name="Focus on improvement" dataDxfId="1" totalsRowDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11D32975-C8F7-4E4C-9DCB-E1DD0F4EF809}" name="Table1" displayName="Table1" ref="A1:H100" totalsRowShown="0" dataDxfId="16">
+  <autoFilter ref="A1:H100" xr:uid="{11D32975-C8F7-4E4C-9DCB-E1DD0F4EF809}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{ECCC568F-30EE-4B6A-B426-3426F99425E7}" name="Attempts" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{16429E15-314C-4930-A463-A56B94D5D37F}" name="Phases" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{EA75679D-0C9D-4438-A7AA-74FB81AF92ED}" name="Result" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{BA7551D7-01AC-42E1-A8FB-050E702D3911}" name="Cause of Death" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{87E6156D-9D22-48BA-909B-ED2CF9E0F3B4}" name="Resurrection used?" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{232FD259-656D-4902-889A-854F57D8DE67}" name="improvement focus" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{339EFA48-67A1-40AF-9197-8C986340ED84}" name="How well I applied it" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{3DC2DC4C-0FCA-42C8-8CBF-7E73E8B7E9D8}" name="Furthest Phase" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -514,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C53C21-1371-4E9E-994E-33547CDE1C18}">
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
@@ -523,9 +570,11 @@
     <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -542,234 +591,536 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
+      <c r="E3" s="1">
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -778,8 +1129,10 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -788,8 +1141,10 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -798,8 +1153,10 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -808,8 +1165,10 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -818,8 +1177,10 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -828,8 +1189,10 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -838,8 +1201,10 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -848,8 +1213,10 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -858,8 +1225,10 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -868,8 +1237,10 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -878,8 +1249,10 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -888,8 +1261,10 @@
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -898,8 +1273,10 @@
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -908,8 +1285,10 @@
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -918,8 +1297,10 @@
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -928,8 +1309,10 @@
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -938,8 +1321,10 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>39</v>
       </c>
@@ -948,8 +1333,10 @@
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>40</v>
       </c>
@@ -958,8 +1345,10 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>41</v>
       </c>
@@ -968,8 +1357,10 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>42</v>
       </c>
@@ -978,8 +1369,10 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>43</v>
       </c>
@@ -988,8 +1381,10 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>44</v>
       </c>
@@ -998,8 +1393,10 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45</v>
       </c>
@@ -1008,8 +1405,10 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -1018,8 +1417,10 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>47</v>
       </c>
@@ -1028,8 +1429,10 @@
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>48</v>
       </c>
@@ -1038,8 +1441,10 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>49</v>
       </c>
@@ -1048,8 +1453,10 @@
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>50</v>
       </c>
@@ -1058,8 +1465,10 @@
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>51</v>
       </c>
@@ -1068,8 +1477,10 @@
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>52</v>
       </c>
@@ -1078,8 +1489,10 @@
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>53</v>
       </c>
@@ -1088,8 +1501,10 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>54</v>
       </c>
@@ -1098,8 +1513,10 @@
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>55</v>
       </c>
@@ -1108,8 +1525,10 @@
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>56</v>
       </c>
@@ -1118,8 +1537,10 @@
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>57</v>
       </c>
@@ -1128,8 +1549,10 @@
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>58</v>
       </c>
@@ -1138,8 +1561,10 @@
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>59</v>
       </c>
@@ -1148,8 +1573,10 @@
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>60</v>
       </c>
@@ -1158,8 +1585,10 @@
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>61</v>
       </c>
@@ -1168,8 +1597,10 @@
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>62</v>
       </c>
@@ -1178,8 +1609,10 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>63</v>
       </c>
@@ -1188,8 +1621,10 @@
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>64</v>
       </c>
@@ -1198,8 +1633,10 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>65</v>
       </c>
@@ -1208,8 +1645,10 @@
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>66</v>
       </c>
@@ -1218,8 +1657,10 @@
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>67</v>
       </c>
@@ -1228,8 +1669,10 @@
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>68</v>
       </c>
@@ -1238,8 +1681,10 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>69</v>
       </c>
@@ -1248,8 +1693,10 @@
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>70</v>
       </c>
@@ -1258,8 +1705,10 @@
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>71</v>
       </c>
@@ -1268,8 +1717,10 @@
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>72</v>
       </c>
@@ -1278,8 +1729,10 @@
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>73</v>
       </c>
@@ -1288,8 +1741,10 @@
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>74</v>
       </c>
@@ -1298,8 +1753,10 @@
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>75</v>
       </c>
@@ -1308,8 +1765,10 @@
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>76</v>
       </c>
@@ -1318,8 +1777,10 @@
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>77</v>
       </c>
@@ -1328,8 +1789,10 @@
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>78</v>
       </c>
@@ -1338,8 +1801,10 @@
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>79</v>
       </c>
@@ -1348,8 +1813,10 @@
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>80</v>
       </c>
@@ -1358,8 +1825,10 @@
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>81</v>
       </c>
@@ -1368,8 +1837,10 @@
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>82</v>
       </c>
@@ -1378,8 +1849,10 @@
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>83</v>
       </c>
@@ -1388,8 +1861,10 @@
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>84</v>
       </c>
@@ -1398,8 +1873,10 @@
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>85</v>
       </c>
@@ -1408,8 +1885,10 @@
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>86</v>
       </c>
@@ -1418,8 +1897,10 @@
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>87</v>
       </c>
@@ -1428,8 +1909,10 @@
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>88</v>
       </c>
@@ -1438,8 +1921,10 @@
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>89</v>
       </c>
@@ -1448,8 +1933,10 @@
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>90</v>
       </c>
@@ -1458,8 +1945,10 @@
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>91</v>
       </c>
@@ -1468,8 +1957,10 @@
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>92</v>
       </c>
@@ -1478,8 +1969,10 @@
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>93</v>
       </c>
@@ -1488,8 +1981,10 @@
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>94</v>
       </c>
@@ -1498,8 +1993,10 @@
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>95</v>
       </c>
@@ -1508,8 +2005,10 @@
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>96</v>
       </c>
@@ -1518,8 +2017,10 @@
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>97</v>
       </c>
@@ -1528,8 +2029,10 @@
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>98</v>
       </c>
@@ -1538,8 +2041,10 @@
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>99</v>
       </c>
@@ -1548,8 +2053,10 @@
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>100</v>
       </c>
@@ -1558,8 +2065,36 @@
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
     </row>
   </sheetData>
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B101:B1048576" xr:uid="{61843CEF-EFBA-44F5-9414-6F8A01093FF9}">
+      <formula1>$B:$B</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B100" xr:uid="{9AF36983-0ACE-4728-BEC4-25A905961FE4}">
+      <formula1>"Phase 0, Phase 1, Phase 2, Phase 3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C100" xr:uid="{DE3B8F30-C28A-4F35-9841-3A098AA31EE6}">
+      <formula1>"Victory,Defeat"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D100" xr:uid="{F5D13980-EE70-4FCB-BE6B-B553A0EAB3B3}">
+      <formula1>"Missed deflection,Failed Mikiri Counter,Missed dodge,Failed sweep counter,Failed lightning reversal,Posture broken,Other/Unknown,N/A"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E100" xr:uid="{14BE126B-2B67-4DE1-9EB9-07DE07688801}">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F100" xr:uid="{CED262F7-08EA-45A4-9900-B1D7D16C98B7}">
+      <formula1>"Deflections,Mikiri Counters,Sweep attacks,General Survival,Lightning reversals,Posture management,Attack openings,N/A"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G100" xr:uid="{1ECEE265-0A2B-4FEC-8931-413AAC7A2007}">
+      <formula1>"Good,Partial,Poor,N/A"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H100" xr:uid="{AA7560FD-EEC1-4D04-910F-62396DD19E12}">
+      <formula1>"Phase 0,Phase 1,Phase 2,Phase 3"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1576,15 +2111,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009C2E8180AE34A74AA7D955D516D7D11F" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="032f417f655511d96504b6628d5b28cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2b855ca2-f08e-416a-ba22-5733a5e836cb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdaeacb9f6b7a99b7aabcaa729afd845" ns3:_="">
     <xsd:import namespace="2b855ca2-f08e-416a-ba22-5733a5e836cb"/>
@@ -1760,6 +2286,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDF25203-5EAB-4C9B-80A0-6EA1A2223B49}">
   <ds:schemaRefs>
@@ -1777,14 +2312,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1905C0C6-0920-4BA2-ABAC-2C543CE3EACC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0290E46F-7474-4DAD-8FDF-DA450DE2263D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1800,4 +2327,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1905C0C6-0920-4BA2-ABAC-2C543CE3EACC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Data100.xlsx
+++ b/Data100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kechi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6675555-13B7-4DBC-B58C-3728944D0F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76DA64FE-E6D5-472D-B169-8F3FFED84D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{131766D7-03E8-4ABE-966F-E54EA5032F95}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="25">
   <si>
     <t>Attempts</t>
   </si>
@@ -1124,229 +1124,495 @@
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>39</v>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>40</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
@@ -2070,9 +2336,6 @@
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B101:B1048576" xr:uid="{61843CEF-EFBA-44F5-9414-6F8A01093FF9}">
-      <formula1>$B:$B</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B100" xr:uid="{9AF36983-0ACE-4728-BEC4-25A905961FE4}">
       <formula1>"Phase 0, Phase 1, Phase 2, Phase 3"</formula1>
     </dataValidation>
@@ -2082,9 +2345,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D100" xr:uid="{F5D13980-EE70-4FCB-BE6B-B553A0EAB3B3}">
       <formula1>"Missed deflection,Failed Mikiri Counter,Missed dodge,Failed sweep counter,Failed lightning reversal,Posture broken,Other/Unknown,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E100" xr:uid="{14BE126B-2B67-4DE1-9EB9-07DE07688801}">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F100" xr:uid="{CED262F7-08EA-45A4-9900-B1D7D16C98B7}">
       <formula1>"Deflections,Mikiri Counters,Sweep attacks,General Survival,Lightning reversals,Posture management,Attack openings,N/A"</formula1>
     </dataValidation>
@@ -2093,6 +2353,12 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H100" xr:uid="{AA7560FD-EEC1-4D04-910F-62396DD19E12}">
       <formula1>"Phase 0,Phase 1,Phase 2,Phase 3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B101:B1048576" xr:uid="{61843CEF-EFBA-44F5-9414-6F8A01093FF9}">
+      <formula1>$B:$B</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E34:E100 E2:E32" xr:uid="{14BE126B-2B67-4DE1-9EB9-07DE07688801}">
+      <formula1>"0,1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2111,6 +2377,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009C2E8180AE34A74AA7D955D516D7D11F" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="032f417f655511d96504b6628d5b28cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2b855ca2-f08e-416a-ba22-5733a5e836cb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdaeacb9f6b7a99b7aabcaa729afd845" ns3:_="">
     <xsd:import namespace="2b855ca2-f08e-416a-ba22-5733a5e836cb"/>
@@ -2286,15 +2561,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDF25203-5EAB-4C9B-80A0-6EA1A2223B49}">
   <ds:schemaRefs>
@@ -2312,6 +2578,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1905C0C6-0920-4BA2-ABAC-2C543CE3EACC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0290E46F-7474-4DAD-8FDF-DA450DE2263D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2327,12 +2601,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1905C0C6-0920-4BA2-ABAC-2C543CE3EACC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>